--- a/VitalSigns/TestBuild/StructureDefinition-no-domain-VitalSigns-Observation-respirationrate.xlsx
+++ b/VitalSigns/TestBuild/StructureDefinition-no-domain-VitalSigns-Observation-respirationrate.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.1</t>
+    <t>0.9.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -390,7 +390,7 @@
     <t>A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -620,7 +620,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(CarePlan|DeviceRequest|ImmunizationRecommendation|MedicationRequest|NutritionOrder|ServiceRequest)
+    <t xml:space="preserve">Reference(CarePlan|4.0.1|DeviceRequest|4.0.1|ImmunizationRecommendation|4.0.1|MedicationRequest|4.0.1|NutritionOrder|4.0.1|ServiceRequest|4.0.1)
 </t>
   </si>
   <si>
@@ -649,7 +649,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(MedicationAdministration|MedicationDispense|MedicationStatement|Procedure|Immunization|ImagingStudy)
+    <t xml:space="preserve">Reference(MedicationAdministration|4.0.1|MedicationDispense|4.0.1|MedicationStatement|4.0.1|Procedure|4.0.1|Immunization|4.0.1|ImagingStudy|4.0.1)
 </t>
   </si>
   <si>
@@ -729,7 +729,7 @@
     <t>Codes for high level observation categories.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-category</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-category|4.0.1</t>
   </si>
   <si>
     <t>value:coding.code}
@@ -1019,7 +1019,7 @@
     <t>This identifies the vital sign result type.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-vitalsignresult</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-vitalsignresult|4.0.1</t>
   </si>
   <si>
     <t>Event.code</t>
@@ -1177,7 +1177,7 @@
     <t>Observation.focus</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Resource)
+    <t xml:space="preserve">Reference(Resource|4.0.1)
 </t>
   </si>
   <si>
@@ -1200,7 +1200,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Encounter)
+    <t xml:space="preserve">Reference(Encounter|4.0.1)
 </t>
   </si>
   <si>
@@ -1299,7 +1299,7 @@
     <t>Observation.performer</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Practitioner|PractitionerRole|Organization|CareTeam|Patient|RelatedPerson)
+    <t xml:space="preserve">Reference(Practitioner|4.0.1|PractitionerRole|4.0.1|Organization|4.0.1|CareTeam|4.0.1|Patient|4.0.1|RelatedPerson|4.0.1)
 </t>
   </si>
   <si>
@@ -1567,7 +1567,7 @@
     <t>Codes specifying why the result (`Observation.value[x]`) is missing.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/data-absent-reason</t>
+    <t>http://hl7.org/fhir/ValueSet/data-absent-reason|4.0.1</t>
   </si>
   <si>
     <t>obs-6
@@ -1599,7 +1599,7 @@
     <t>Codes identifying interpretations of observations.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-interpretation</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-interpretation|4.0.1</t>
   </si>
   <si>
     <t>&lt; 260245000 |Findings values|</t>
@@ -1658,7 +1658,7 @@
     <t>Codes describing anatomical locations. May include laterality.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/body-site</t>
+    <t>http://hl7.org/fhir/ValueSet/body-site|4.0.1</t>
   </si>
   <si>
     <t>&lt; 123037004 |Body structure|</t>
@@ -1691,7 +1691,7 @@
     <t>Methods for simple observations.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-methods</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-methods|4.0.1</t>
   </si>
   <si>
     <t>OBX-17</t>
@@ -1703,7 +1703,7 @@
     <t>Observation.specimen</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Specimen)
+    <t xml:space="preserve">Reference(Specimen|4.0.1)
 </t>
   </si>
   <si>
@@ -1731,7 +1731,7 @@
     <t>Observation.device</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Device|DeviceMetric)
+    <t xml:space="preserve">Reference(Device|4.0.1|DeviceMetric|4.0.1)
 </t>
   </si>
   <si>
@@ -1811,7 +1811,7 @@
     <t>Observation.referenceRange.low</t>
   </si>
   <si>
-    <t xml:space="preserve">Quantity {SimpleQuantity}
+    <t xml:space="preserve">Quantity {SimpleQuantity|4.0.1}
 </t>
   </si>
   <si>
@@ -1861,7 +1861,7 @@
     <t>Code for the meaning of a reference range.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/referencerange-meaning</t>
+    <t>http://hl7.org/fhir/ValueSet/referencerange-meaning|4.0.1</t>
   </si>
   <si>
     <t>&lt; 260245000 |Findings values| OR  @@ -1894,7 +1894,7 @@
     <t>Codes identifying the population the reference range applies to.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/referencerange-appliesto</t>
+    <t>http://hl7.org/fhir/ValueSet/referencerange-appliesto|4.0.1</t>
   </si>
   <si>
     <t>Observation.referenceRange.age</t>
@@ -1931,7 +1931,7 @@
     <t>Observation.hasMember</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(QuestionnaireResponse|MolecularSequence|vitalsigns)
+    <t xml:space="preserve">Reference(QuestionnaireResponse|4.0.1|MolecularSequence|4.0.1|vitalsigns|4.0.1)
 </t>
   </si>
   <si>
@@ -1953,7 +1953,7 @@
     <t>Observation.derivedFrom</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(DocumentReference|ImagingStudy|Media|QuestionnaireResponse|MolecularSequence|vitalsigns)
+    <t xml:space="preserve">Reference(DocumentReference|4.0.1|ImagingStudy|4.0.1|Media|4.0.1|QuestionnaireResponse|4.0.1|MolecularSequence|4.0.1|vitalsigns|4.0.1)
 </t>
   </si>
   <si>
@@ -2423,7 +2423,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="54.6171875" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="43.5859375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="47.9921875" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
@@ -4845,7 +4845,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="21" hidden="true">
+    <row r="21">
       <c r="A21" t="s" s="2">
         <v>207</v>
       </c>
@@ -5085,7 +5085,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="23" hidden="true">
+    <row r="23">
       <c r="A23" t="s" s="2">
         <v>230</v>
       </c>
@@ -5447,7 +5447,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="26" hidden="true">
+    <row r="26">
       <c r="A26" t="s" s="2">
         <v>245</v>
       </c>
@@ -5807,7 +5807,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="29" hidden="true">
+    <row r="29">
       <c r="A29" t="s" s="2">
         <v>259</v>
       </c>
@@ -6049,7 +6049,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="31" hidden="true">
+    <row r="31">
       <c r="A31" t="s" s="2">
         <v>277</v>
       </c>
@@ -6533,7 +6533,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="35" hidden="true">
+    <row r="35">
       <c r="A35" t="s" s="2">
         <v>313</v>
       </c>
@@ -9067,7 +9067,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="56" hidden="true">
+    <row r="56">
       <c r="A56" t="s" s="2">
         <v>362</v>
       </c>
@@ -9431,7 +9431,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="59" hidden="true">
+    <row r="59">
       <c r="A59" t="s" s="2">
         <v>389</v>
       </c>
@@ -10155,7 +10155,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="65" hidden="true">
+    <row r="65">
       <c r="A65" t="s" s="2">
         <v>438</v>
       </c>
@@ -10517,7 +10517,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="68" hidden="true">
+    <row r="68">
       <c r="A68" t="s" s="2">
         <v>445</v>
       </c>
@@ -10761,7 +10761,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="70" hidden="true">
+    <row r="70">
       <c r="A70" t="s" s="2">
         <v>466</v>
       </c>
@@ -10881,7 +10881,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="71" hidden="true">
+    <row r="71">
       <c r="A71" t="s" s="2">
         <v>474</v>
       </c>
@@ -11001,7 +11001,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="72" hidden="true">
+    <row r="72">
       <c r="A72" t="s" s="2">
         <v>483</v>
       </c>
@@ -11123,7 +11123,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="73" hidden="true">
+    <row r="73">
       <c r="A73" t="s" s="2">
         <v>491</v>
       </c>
@@ -13411,7 +13411,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="92" hidden="true">
+    <row r="92">
       <c r="A92" t="s" s="2">
         <v>624</v>
       </c>
@@ -13893,7 +13893,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="96" hidden="true">
+    <row r="96">
       <c r="A96" t="s" s="2">
         <v>634</v>
       </c>
@@ -14015,7 +14015,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="97" hidden="true">
+    <row r="97">
       <c r="A97" t="s" s="2">
         <v>640</v>
       </c>
@@ -14137,7 +14137,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="98" hidden="true">
+    <row r="98">
       <c r="A98" t="s" s="2">
         <v>649</v>
       </c>
@@ -14505,12 +14505,12 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:AP100">
-    <filterColumn colId="6">
+    <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
       </customFilters>
     </filterColumn>
-    <filterColumn colId="26">
+    <filterColumn colId="27">
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>

--- a/VitalSigns/TestBuild/StructureDefinition-no-domain-VitalSigns-Observation-respirationrate.xlsx
+++ b/VitalSigns/TestBuild/StructureDefinition-no-domain-VitalSigns-Observation-respirationrate.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.0</t>
+    <t>1.0.0</t>
   </si>
   <si>
     <t>Name</t>

--- a/VitalSigns/TestBuild/StructureDefinition-no-domain-VitalSigns-Observation-respirationrate.xlsx
+++ b/VitalSigns/TestBuild/StructureDefinition-no-domain-VitalSigns-Observation-respirationrate.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.0</t>
+    <t>0.9.5</t>
   </si>
   <si>
     <t>Name</t>

--- a/VitalSigns/TestBuild/StructureDefinition-no-domain-VitalSigns-Observation-respirationrate.xlsx
+++ b/VitalSigns/TestBuild/StructureDefinition-no-domain-VitalSigns-Observation-respirationrate.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.5</t>
+    <t>0.9.6</t>
   </si>
   <si>
     <t>Name</t>

--- a/VitalSigns/TestBuild/StructureDefinition-no-domain-VitalSigns-Observation-respirationrate.xlsx
+++ b/VitalSigns/TestBuild/StructureDefinition-no-domain-VitalSigns-Observation-respirationrate.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.6</t>
+    <t>0.9.61</t>
   </si>
   <si>
     <t>Name</t>

--- a/VitalSigns/TestBuild/StructureDefinition-no-domain-VitalSigns-Observation-respirationrate.xlsx
+++ b/VitalSigns/TestBuild/StructureDefinition-no-domain-VitalSigns-Observation-respirationrate.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.61</t>
+    <t>0.9.71</t>
   </si>
   <si>
     <t>Name</t>

--- a/VitalSigns/TestBuild/StructureDefinition-no-domain-VitalSigns-Observation-respirationrate.xlsx
+++ b/VitalSigns/TestBuild/StructureDefinition-no-domain-VitalSigns-Observation-respirationrate.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.71</t>
+    <t>0.9.72</t>
   </si>
   <si>
     <t>Name</t>

--- a/VitalSigns/TestBuild/StructureDefinition-no-domain-VitalSigns-Observation-respirationrate.xlsx
+++ b/VitalSigns/TestBuild/StructureDefinition-no-domain-VitalSigns-Observation-respirationrate.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.72</t>
+    <t>0.9.73</t>
   </si>
   <si>
     <t>Name</t>

--- a/VitalSigns/TestBuild/StructureDefinition-no-domain-VitalSigns-Observation-respirationrate.xlsx
+++ b/VitalSigns/TestBuild/StructureDefinition-no-domain-VitalSigns-Observation-respirationrate.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.73</t>
+    <t>0.9.74</t>
   </si>
   <si>
     <t>Name</t>

--- a/VitalSigns/TestBuild/StructureDefinition-no-domain-VitalSigns-Observation-respirationrate.xlsx
+++ b/VitalSigns/TestBuild/StructureDefinition-no-domain-VitalSigns-Observation-respirationrate.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.74</t>
+    <t>0.9.2</t>
   </si>
   <si>
     <t>Name</t>

--- a/VitalSigns/TestBuild/StructureDefinition-no-domain-VitalSigns-Observation-respirationrate.xlsx
+++ b/VitalSigns/TestBuild/StructureDefinition-no-domain-VitalSigns-Observation-respirationrate.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.2</t>
+    <t>0.9.74</t>
   </si>
   <si>
     <t>Name</t>
